--- a/template_posto.xlsx
+++ b/template_posto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moise\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995B82FF-32E7-4CEB-9153-76E6BB58891F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA568BD-8870-49F0-B6C2-39F10BB00BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F2E926A6-1D7B-46C1-853C-913B9CD95B80}"/>
   </bookViews>
@@ -18,7 +18,6 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="\a">#REF!</definedName>
@@ -3262,2293 +3261,6 @@
       <sheetData sheetId="45"/>
       <sheetData sheetId="46"/>
       <sheetData sheetId="47"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="PADRÃO"/>
-      <sheetName val="FLUXO DE EDIÇÃO"/>
-      <sheetName val="FORNECEDORES"/>
-      <sheetName val="CADASTRO"/>
-      <sheetName val="AGUIAR"/>
-      <sheetName val="MARV"/>
-      <sheetName val="RESUMOS --&gt;"/>
-      <sheetName val="RES. GERAL"/>
-      <sheetName val="TQ01"/>
-      <sheetName val="TQ03"/>
-      <sheetName val="TQ04"/>
-      <sheetName val="100C"/>
-      <sheetName val="RTN"/>
-      <sheetName val="SERV"/>
-      <sheetName val="RZD"/>
-      <sheetName val="BOA"/>
-      <sheetName val="JAG"/>
-      <sheetName val="BETUME"/>
-      <sheetName val="TCM04"/>
-      <sheetName val="PRODUÇÃO"/>
-      <sheetName val="TB PROD-OUT-23"/>
-      <sheetName val="CB`S COPA"/>
-      <sheetName val="DIVERSOS"/>
-      <sheetName val="ASFALTO"/>
-      <sheetName val="FINANCEIRO"/>
-      <sheetName val="CAÇ COPA --&gt;"/>
-      <sheetName val="CB11"/>
-      <sheetName val="CB12"/>
-      <sheetName val="CB13"/>
-      <sheetName val="CB15"/>
-      <sheetName val="CB16"/>
-      <sheetName val="CB18"/>
-      <sheetName val="CB19"/>
-      <sheetName val="CT03"/>
-      <sheetName val="CAÇ TERCEIROS)"/>
-      <sheetName val="CB23"/>
-      <sheetName val="CB24"/>
-      <sheetName val="CB25"/>
-      <sheetName val="CB29"/>
-      <sheetName val="CB30"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>TQ01</v>
-          </cell>
-          <cell r="C9"/>
-          <cell r="D9" t="str">
-            <v>TANQUE EUSÉBIO - COPA</v>
-          </cell>
-          <cell r="E9" t="str">
-            <v>JJUNIOR</v>
-          </cell>
-          <cell r="F9"/>
-          <cell r="G9"/>
-          <cell r="H9"/>
-          <cell r="I9"/>
-          <cell r="J9"/>
-          <cell r="K9"/>
-          <cell r="L9"/>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>FO01</v>
-          </cell>
-          <cell r="C10"/>
-          <cell r="D10" t="str">
-            <v>POSTO SERV 100 EUSÉBIO</v>
-          </cell>
-          <cell r="E10" t="str">
-            <v>07.295.702/0001-99</v>
-          </cell>
-          <cell r="F10" t="str">
-            <v>SERVI 100 COMERCIO DE COMBUSTIVEIS LTDA</v>
-          </cell>
-          <cell r="G10"/>
-          <cell r="H10"/>
-          <cell r="I10"/>
-          <cell r="J10"/>
-          <cell r="K10"/>
-          <cell r="L10"/>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>FO02</v>
-          </cell>
-          <cell r="C11"/>
-          <cell r="D11" t="str">
-            <v>POSTO MAROVINO</v>
-          </cell>
-          <cell r="E11" t="str">
-            <v>51.605.555/0001-06</v>
-          </cell>
-          <cell r="F11" t="str">
-            <v>POSTO MAROVINO LTDA</v>
-          </cell>
-          <cell r="G11" t="str">
-            <v>(88) 99606-0501</v>
-          </cell>
-          <cell r="H11" t="str">
-            <v>B. do BRASIL</v>
-          </cell>
-          <cell r="I11" t="str">
-            <v>1157-6</v>
-          </cell>
-          <cell r="J11" t="str">
-            <v>53442-0</v>
-          </cell>
-          <cell r="K11" t="str">
-            <v>CORRENTE</v>
-          </cell>
-          <cell r="L11">
-            <v>51605555000106</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>FO03</v>
-          </cell>
-          <cell r="C12"/>
-          <cell r="D12" t="str">
-            <v>POSTO REZENDE SOBRAL</v>
-          </cell>
-          <cell r="E12"/>
-          <cell r="F12"/>
-          <cell r="G12"/>
-          <cell r="H12"/>
-          <cell r="I12"/>
-          <cell r="J12"/>
-          <cell r="K12"/>
-          <cell r="L12"/>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>FO04</v>
-          </cell>
-          <cell r="C13"/>
-          <cell r="D13" t="str">
-            <v>POSTO BOAVENTURA FORTALEZA</v>
-          </cell>
-          <cell r="E13"/>
-          <cell r="F13"/>
-          <cell r="G13"/>
-          <cell r="H13"/>
-          <cell r="I13"/>
-          <cell r="J13"/>
-          <cell r="K13"/>
-          <cell r="L13"/>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>FO05</v>
-          </cell>
-          <cell r="C14"/>
-          <cell r="D14" t="str">
-            <v>POSTO AGUIAR UBAÚNA</v>
-          </cell>
-          <cell r="E14" t="str">
-            <v>11575650/0001-81</v>
-          </cell>
-          <cell r="F14" t="str">
-            <v>POSTO DE COMBUSTIVEIS AGUIAR LTDA</v>
-          </cell>
-          <cell r="G14" t="str">
-            <v>(88) 99990-0224</v>
-          </cell>
-          <cell r="H14" t="str">
-            <v>B. do BRASIL</v>
-          </cell>
-          <cell r="I14" t="str">
-            <v>5663-4</v>
-          </cell>
-          <cell r="J14" t="str">
-            <v>10905-3</v>
-          </cell>
-          <cell r="K14" t="str">
-            <v>CORRENTE</v>
-          </cell>
-          <cell r="L14"/>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>FO06</v>
-          </cell>
-          <cell r="C15"/>
-          <cell r="D15" t="str">
-            <v>POSTO RETORNO LTDA</v>
-          </cell>
-          <cell r="E15"/>
-          <cell r="F15"/>
-          <cell r="G15"/>
-          <cell r="H15"/>
-          <cell r="I15"/>
-          <cell r="J15"/>
-          <cell r="K15"/>
-          <cell r="L15"/>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>FO07</v>
-          </cell>
-          <cell r="C16"/>
-          <cell r="D16" t="str">
-            <v>POSTO SANTO ANTÔNIO JAGUARETAMA</v>
-          </cell>
-          <cell r="E16"/>
-          <cell r="F16"/>
-          <cell r="G16"/>
-          <cell r="H16"/>
-          <cell r="I16"/>
-          <cell r="J16"/>
-          <cell r="K16"/>
-          <cell r="L16"/>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>TQ03</v>
-          </cell>
-          <cell r="C17"/>
-          <cell r="D17" t="str">
-            <v>TANQUE TETRAOIL 03 U3</v>
-          </cell>
-          <cell r="E17"/>
-          <cell r="F17"/>
-          <cell r="G17"/>
-          <cell r="H17"/>
-          <cell r="I17"/>
-          <cell r="J17"/>
-          <cell r="K17"/>
-          <cell r="L17"/>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>TQ04</v>
-          </cell>
-          <cell r="C18"/>
-          <cell r="D18" t="str">
-            <v>TANQUE TETRAOIL EDMIL</v>
-          </cell>
-          <cell r="E18"/>
-          <cell r="F18"/>
-          <cell r="G18"/>
-          <cell r="H18"/>
-          <cell r="I18"/>
-          <cell r="J18"/>
-          <cell r="K18"/>
-          <cell r="L18"/>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>FO08</v>
-          </cell>
-          <cell r="C19"/>
-          <cell r="D19" t="str">
-            <v>POSTO 100 POR CENTO</v>
-          </cell>
-          <cell r="E19" t="str">
-            <v>48.688.944/0002-00</v>
-          </cell>
-          <cell r="F19" t="str">
-            <v>COMERCIAL DE COMBUSTIVEIS CEM POR CENTO LTDA</v>
-          </cell>
-          <cell r="G19" t="str">
-            <v>---</v>
-          </cell>
-          <cell r="H19" t="str">
-            <v>---</v>
-          </cell>
-          <cell r="I19" t="str">
-            <v>---</v>
-          </cell>
-          <cell r="J19" t="str">
-            <v>---</v>
-          </cell>
-          <cell r="K19" t="str">
-            <v>---</v>
-          </cell>
-          <cell r="L19" t="str">
-            <v>---</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20"/>
-          <cell r="C20"/>
-          <cell r="D20"/>
-          <cell r="E20"/>
-          <cell r="F20"/>
-          <cell r="G20"/>
-          <cell r="H20"/>
-          <cell r="I20"/>
-          <cell r="J20"/>
-          <cell r="K20"/>
-          <cell r="L20"/>
-        </row>
-        <row r="21">
-          <cell r="B21"/>
-          <cell r="C21"/>
-          <cell r="E21"/>
-          <cell r="F21"/>
-          <cell r="G21"/>
-          <cell r="H21"/>
-          <cell r="I21"/>
-          <cell r="J21"/>
-          <cell r="K21"/>
-          <cell r="L21"/>
-        </row>
-        <row r="22">
-          <cell r="B22"/>
-          <cell r="C22"/>
-          <cell r="D22"/>
-          <cell r="E22"/>
-          <cell r="F22"/>
-          <cell r="G22"/>
-          <cell r="H22"/>
-          <cell r="I22"/>
-          <cell r="J22"/>
-          <cell r="K22"/>
-          <cell r="L22"/>
-        </row>
-        <row r="23">
-          <cell r="B23"/>
-          <cell r="C23"/>
-          <cell r="D23"/>
-          <cell r="E23"/>
-          <cell r="F23"/>
-          <cell r="G23"/>
-          <cell r="H23"/>
-          <cell r="I23"/>
-          <cell r="J23"/>
-          <cell r="K23"/>
-          <cell r="L23"/>
-        </row>
-        <row r="24">
-          <cell r="B24"/>
-          <cell r="C24"/>
-          <cell r="D24"/>
-          <cell r="E24"/>
-          <cell r="F24"/>
-          <cell r="G24"/>
-          <cell r="H24"/>
-          <cell r="I24"/>
-          <cell r="J24"/>
-          <cell r="K24"/>
-          <cell r="L24"/>
-        </row>
-        <row r="25">
-          <cell r="B25"/>
-          <cell r="C25"/>
-          <cell r="D25"/>
-          <cell r="E25"/>
-          <cell r="F25"/>
-          <cell r="G25"/>
-          <cell r="H25"/>
-          <cell r="I25"/>
-          <cell r="J25"/>
-          <cell r="K25"/>
-          <cell r="L25"/>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>T-CM04</v>
-          </cell>
-          <cell r="C26" t="str">
-            <v>T-PNX8017</v>
-          </cell>
-          <cell r="D26" t="str">
-            <v>TANQUE ABAST. CM04</v>
-          </cell>
-          <cell r="E26" t="str">
-            <v>CÉLIO</v>
-          </cell>
-          <cell r="F26"/>
-          <cell r="G26" t="str">
-            <v>COPA ENGENHARIA</v>
-          </cell>
-          <cell r="H26"/>
-          <cell r="I26"/>
-          <cell r="J26"/>
-          <cell r="K26"/>
-          <cell r="L26"/>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>T-CM05</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v>T-OHX2270</v>
-          </cell>
-          <cell r="D27" t="str">
-            <v>TANQUE ABAST. CM05</v>
-          </cell>
-          <cell r="E27" t="str">
-            <v>CÉLIO</v>
-          </cell>
-          <cell r="F27"/>
-          <cell r="G27" t="str">
-            <v>COPA ENGENHARIA</v>
-          </cell>
-          <cell r="H27"/>
-          <cell r="I27"/>
-          <cell r="J27"/>
-          <cell r="K27"/>
-          <cell r="L27"/>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>T-CMMM</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>T-MELOSA MM</v>
-          </cell>
-          <cell r="D28" t="str">
-            <v>TANQUE ABAST. MARCO MONTE</v>
-          </cell>
-          <cell r="E28" t="str">
-            <v>WAGNER</v>
-          </cell>
-          <cell r="F28"/>
-          <cell r="G28" t="str">
-            <v>MARCO MONTE</v>
-          </cell>
-          <cell r="H28"/>
-          <cell r="I28"/>
-          <cell r="J28"/>
-          <cell r="K28"/>
-          <cell r="L28"/>
-        </row>
-        <row r="29">
-          <cell r="B29"/>
-          <cell r="C29"/>
-          <cell r="D29"/>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>PREFIXO</v>
-          </cell>
-          <cell r="C30"/>
-          <cell r="D30" t="str">
-            <v>EQUIPAMENTO</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31"/>
-          <cell r="C31"/>
-          <cell r="D31"/>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>CB10</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>OZA3176</v>
-          </cell>
-          <cell r="D32" t="str">
-            <v>CB COPA</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>CB11</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>OSP9850</v>
-          </cell>
-          <cell r="D33" t="str">
-            <v>CB COPA</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>CB12</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>PNX5G67</v>
-          </cell>
-          <cell r="D34" t="str">
-            <v>CB COPA</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>CB13</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>POK2486</v>
-          </cell>
-          <cell r="D35" t="str">
-            <v>CB COPA</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>CB14</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v>PON7E59</v>
-          </cell>
-          <cell r="D36" t="str">
-            <v>CB COPA</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="str">
-            <v>CB15</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>PON9D53</v>
-          </cell>
-          <cell r="D37" t="str">
-            <v>CB COPA</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="str">
-            <v>CB16</v>
-          </cell>
-          <cell r="C38" t="str">
-            <v>PON9G13</v>
-          </cell>
-          <cell r="D38" t="str">
-            <v>CB COPA</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39" t="str">
-            <v>CB18</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v>SBP6D64</v>
-          </cell>
-          <cell r="D39" t="str">
-            <v>CB COPA</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40" t="str">
-            <v>CB19</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v>THT3E02</v>
-          </cell>
-          <cell r="D40" t="str">
-            <v>CB COPA</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41"/>
-          <cell r="C41"/>
-          <cell r="D41"/>
-        </row>
-        <row r="42">
-          <cell r="B42"/>
-          <cell r="C42"/>
-          <cell r="D42"/>
-        </row>
-        <row r="43">
-          <cell r="B43" t="str">
-            <v>PREFIXO</v>
-          </cell>
-          <cell r="C43"/>
-          <cell r="D43" t="str">
-            <v>EQUIPAMENTO</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44"/>
-          <cell r="C44"/>
-          <cell r="D44"/>
-        </row>
-        <row r="45">
-          <cell r="B45" t="str">
-            <v>CB21</v>
-          </cell>
-          <cell r="C45" t="str">
-            <v>OCG0D83</v>
-          </cell>
-          <cell r="D45" t="str">
-            <v>CAÇAMBA CONE</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46" t="str">
-            <v>CB22</v>
-          </cell>
-          <cell r="C46" t="str">
-            <v>NQW6703</v>
-          </cell>
-          <cell r="D46" t="str">
-            <v>CAÇAMBA CONE</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47" t="str">
-            <v>CB23</v>
-          </cell>
-          <cell r="C47" t="str">
-            <v>NUR7393</v>
-          </cell>
-          <cell r="D47" t="str">
-            <v>CAÇAMBA CONE</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48" t="str">
-            <v>CB24</v>
-          </cell>
-          <cell r="C48" t="str">
-            <v>NYX5J83</v>
-          </cell>
-          <cell r="D48" t="str">
-            <v>CAÇAMBA MARDÔNIO</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49" t="str">
-            <v>CB25</v>
-          </cell>
-          <cell r="C49" t="str">
-            <v>PGP3J02</v>
-          </cell>
-          <cell r="D49" t="str">
-            <v>CAÇAMBA MARDÔNIO</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50" t="str">
-            <v>CB29</v>
-          </cell>
-          <cell r="C50" t="str">
-            <v>MWA3B64</v>
-          </cell>
-          <cell r="D50" t="str">
-            <v>CAÇAMBA MARDÔNIO</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51" t="str">
-            <v>CB30</v>
-          </cell>
-          <cell r="C51" t="str">
-            <v>HKE5275</v>
-          </cell>
-          <cell r="D51" t="str">
-            <v>CAÇAMBA MARDÔNIO</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="B52" t="str">
-            <v>CB26</v>
-          </cell>
-          <cell r="C52" t="str">
-            <v>OCG5G63</v>
-          </cell>
-          <cell r="D52" t="str">
-            <v>CAÇAMBA-LCM 01</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="B53" t="str">
-            <v>CB27</v>
-          </cell>
-          <cell r="C53" t="str">
-            <v>NUY5972</v>
-          </cell>
-          <cell r="D53" t="str">
-            <v>CAÇAMBA-LCM 02</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="B54" t="str">
-            <v>CB28</v>
-          </cell>
-          <cell r="C54" t="str">
-            <v>HWF6B63</v>
-          </cell>
-          <cell r="D54" t="str">
-            <v>CAÇAMBA-ZÉ ILAS</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="B55"/>
-          <cell r="C55"/>
-          <cell r="D55"/>
-        </row>
-        <row r="56">
-          <cell r="B56" t="str">
-            <v>CAÇAMBAS NORDBRITA</v>
-          </cell>
-          <cell r="C56"/>
-          <cell r="D56"/>
-        </row>
-        <row r="57">
-          <cell r="B57" t="str">
-            <v>NB01</v>
-          </cell>
-          <cell r="C57" t="str">
-            <v>PMP6058</v>
-          </cell>
-          <cell r="D57" t="str">
-            <v>CAÇAMBA NORDBRITA</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="B58" t="str">
-            <v>CB ZI 2</v>
-          </cell>
-          <cell r="C58" t="str">
-            <v>CSY9E01</v>
-          </cell>
-          <cell r="D58" t="str">
-            <v>CAÇAMBA 2 ZÉ ILAS</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="B59"/>
-          <cell r="C59"/>
-          <cell r="D59"/>
-        </row>
-        <row r="60">
-          <cell r="B60"/>
-          <cell r="C60"/>
-          <cell r="D60"/>
-        </row>
-        <row r="61">
-          <cell r="B61" t="str">
-            <v>CAÇAMBAS TERCEIROS -SAMARIA</v>
-          </cell>
-          <cell r="C61"/>
-          <cell r="D61"/>
-        </row>
-        <row r="62">
-          <cell r="B62" t="str">
-            <v>CB S1</v>
-          </cell>
-          <cell r="C62" t="str">
-            <v>HYR1B14</v>
-          </cell>
-          <cell r="D62" t="str">
-            <v>CAÇAMBA 1 SAMARIA</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="B63" t="str">
-            <v>CB S2</v>
-          </cell>
-          <cell r="C63" t="str">
-            <v>SBY9B39</v>
-          </cell>
-          <cell r="D63" t="str">
-            <v>CAÇAMBA 1 SAMARIA</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="B64" t="str">
-            <v>CB S3</v>
-          </cell>
-          <cell r="C64" t="str">
-            <v>SBP7J49</v>
-          </cell>
-          <cell r="D64" t="str">
-            <v>CAÇAMBA 1 SAMARIA</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="B65" t="str">
-            <v>CB54</v>
-          </cell>
-          <cell r="C65" t="str">
-            <v>NRC0816</v>
-          </cell>
-          <cell r="D65" t="str">
-            <v>CAÇAMBA 1 SAMARIA</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="B66" t="str">
-            <v>B.T.N.</v>
-          </cell>
-          <cell r="C66" t="str">
-            <v>BI-T-NORD</v>
-          </cell>
-          <cell r="D66" t="str">
-            <v>BI-TRUK NORDIBRITA</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="B67"/>
-          <cell r="C67"/>
-          <cell r="D67"/>
-        </row>
-        <row r="68">
-          <cell r="B68" t="str">
-            <v>EQUIPAMENTOS NO TRECHO</v>
-          </cell>
-          <cell r="C68"/>
-          <cell r="D68"/>
-        </row>
-        <row r="69">
-          <cell r="B69" t="str">
-            <v>LT01</v>
-          </cell>
-          <cell r="C69" t="str">
-            <v>LIMPEZA-TRECHO</v>
-          </cell>
-          <cell r="D69" t="str">
-            <v>LIMP FERRAMENTAS E MESA ACABADORA</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="B70" t="str">
-            <v>RC01</v>
-          </cell>
-          <cell r="C70" t="str">
-            <v>CC142C</v>
-          </cell>
-          <cell r="D70" t="str">
-            <v>ROLO COMP VIBR COMBINADO</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="B71" t="str">
-            <v>RC02</v>
-          </cell>
-          <cell r="C71" t="str">
-            <v>CC142</v>
-          </cell>
-          <cell r="D71" t="str">
-            <v>ROLO COMP VIBR COMBINADO</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="B72" t="str">
-            <v>RP01</v>
-          </cell>
-          <cell r="C72" t="str">
-            <v>SP 8000</v>
-          </cell>
-          <cell r="D72" t="str">
-            <v>ROLO DE PNEUS TEMA SP 8000</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="B73" t="str">
-            <v>RT03</v>
-          </cell>
-          <cell r="C73" t="str">
-            <v>CC1200C</v>
-          </cell>
-          <cell r="D73" t="str">
-            <v>ROLO HAMM HD10</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="B74" t="str">
-            <v>RP02</v>
-          </cell>
-          <cell r="C74" t="str">
-            <v>CP221</v>
-          </cell>
-          <cell r="D74" t="str">
-            <v>ROLO DE PNEUS RP02</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="B75" t="str">
-            <v>RP05</v>
-          </cell>
-          <cell r="C75" t="str">
-            <v>CP1200</v>
-          </cell>
-          <cell r="D75" t="str">
-            <v>ROLO DE PNEUS</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="B76" t="str">
-            <v>RV04</v>
-          </cell>
-          <cell r="C76" t="str">
-            <v>ROLO RV 04</v>
-          </cell>
-          <cell r="D76" t="str">
-            <v>ROLO VIBRATORIO 04</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="B77" t="str">
-            <v>CE03</v>
-          </cell>
-          <cell r="C77" t="str">
-            <v>HEJ6537</v>
-          </cell>
-          <cell r="D77" t="str">
-            <v>CAM. ESPARG.  CE-03</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="B78" t="str">
-            <v>M-CE03</v>
-          </cell>
-          <cell r="C78" t="str">
-            <v>M-HEJ6537</v>
-          </cell>
-          <cell r="D78" t="str">
-            <v>MACARICO ESPARGIDOR CE-03</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="B79" t="str">
-            <v>CE05</v>
-          </cell>
-          <cell r="C79" t="str">
-            <v>OSU4525</v>
-          </cell>
-          <cell r="D79" t="str">
-            <v>CAMINHÃO ESPARGIDOR CE-05</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="B80" t="str">
-            <v>M-CE05</v>
-          </cell>
-          <cell r="C80" t="str">
-            <v>M-OSU4525</v>
-          </cell>
-          <cell r="D80" t="str">
-            <v>MAÇARICO ESPARGIDOR CE-05</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="B81" t="str">
-            <v>CE06</v>
-          </cell>
-          <cell r="C81" t="str">
-            <v>NVB3996</v>
-          </cell>
-          <cell r="D81" t="str">
-            <v>CAMINHÃO ESPARGIDOR CE-06</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="B82" t="str">
-            <v>M-CE06</v>
-          </cell>
-          <cell r="C82" t="str">
-            <v>M-NVB3996</v>
-          </cell>
-          <cell r="D82" t="str">
-            <v>MAÇARICO CE 06</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="B83" t="str">
-            <v>CE04</v>
-          </cell>
-          <cell r="C83" t="str">
-            <v>OSV2854</v>
-          </cell>
-          <cell r="D83" t="str">
-            <v>CAMINHÃO ESPARG CE-04</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="B84" t="str">
-            <v>TCE04</v>
-          </cell>
-          <cell r="C84" t="str">
-            <v>M-OSV2854</v>
-          </cell>
-          <cell r="D84" t="str">
-            <v>MASSARICO ESPARGIDOR CE-04</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="B85" t="str">
-            <v>VA05</v>
-          </cell>
-          <cell r="C85" t="str">
-            <v>VA AF 4000</v>
-          </cell>
-          <cell r="D85" t="str">
-            <v>VIBRO ACABADORA CIBER AF 4000</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="B86" t="str">
-            <v>VA04</v>
-          </cell>
-          <cell r="C86" t="str">
-            <v>VA LEE BOY</v>
-          </cell>
-          <cell r="D86" t="str">
-            <v>VIBRO ACABADORA DE ASFALTO</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="B87" t="str">
-            <v>VA05</v>
-          </cell>
-          <cell r="C87" t="str">
-            <v>VA CIBER 05</v>
-          </cell>
-          <cell r="D87" t="str">
-            <v>VIBRO ACABADORA DE ASFALTO</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="B88" t="str">
-            <v>VA06</v>
-          </cell>
-          <cell r="C88" t="str">
-            <v>VA VOGERE 06</v>
-          </cell>
-          <cell r="D88" t="str">
-            <v>VIBRO ACABADORA DE ASFALTO</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="B89" t="str">
-            <v>VA07</v>
-          </cell>
-          <cell r="C89" t="str">
-            <v>VA DYNAPAC 07</v>
-          </cell>
-          <cell r="D89" t="str">
-            <v>VIBRO ACABADORA DE ASFALTO</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="B90" t="str">
-            <v>RT04</v>
-          </cell>
-          <cell r="C90" t="str">
-            <v>ROLO TANDER</v>
-          </cell>
-          <cell r="D90" t="str">
-            <v>ROLO TANDER</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="B91" t="str">
-            <v>PVIB01</v>
-          </cell>
-          <cell r="C91" t="str">
-            <v>PLACA VIBRATÓRIA</v>
-          </cell>
-          <cell r="D91" t="str">
-            <v>PLACA VIBRATÓRIA</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="B92" t="str">
-            <v>M.O.AP</v>
-          </cell>
-          <cell r="C92" t="str">
-            <v>JQQ0A97</v>
-          </cell>
-          <cell r="D92" t="str">
-            <v>MICRO ÔNIBUS DE APOIO</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="B93" t="str">
-            <v>CR01</v>
-          </cell>
-          <cell r="C93" t="str">
-            <v>SAX8C32</v>
-          </cell>
-          <cell r="D93" t="str">
-            <v>CAMINHÃO REBOQUE</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="B94" t="str">
-            <v>R TERC</v>
-          </cell>
-          <cell r="C94" t="str">
-            <v>RETRO TERC</v>
-          </cell>
-          <cell r="D94" t="str">
-            <v>RETROESCAVADEIRA P/DESCA CARRETA</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="B95"/>
-          <cell r="C95"/>
-          <cell r="D95"/>
-        </row>
-        <row r="96">
-          <cell r="B96" t="str">
-            <v>UA02</v>
-          </cell>
-          <cell r="C96" t="str">
-            <v>USINA 02</v>
-          </cell>
-          <cell r="D96" t="str">
-            <v>USINA  CIBER 02</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="B97" t="str">
-            <v>UA03</v>
-          </cell>
-          <cell r="C97" t="str">
-            <v>USINA 03</v>
-          </cell>
-          <cell r="D97" t="str">
-            <v>USINA TEREX 03</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="B98" t="str">
-            <v>JB02</v>
-          </cell>
-          <cell r="C98" t="str">
-            <v>JUMBO 02</v>
-          </cell>
-          <cell r="D98" t="str">
-            <v>JUMBO CIBER 02</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="B99" t="str">
-            <v>JB03</v>
-          </cell>
-          <cell r="C99" t="str">
-            <v>JUMBO 03</v>
-          </cell>
-          <cell r="D99" t="str">
-            <v>JUMBO TEREX 03</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="B100" t="str">
-            <v>PC04</v>
-          </cell>
-          <cell r="C100" t="str">
-            <v>924 K 04</v>
-          </cell>
-          <cell r="D100" t="str">
-            <v>PÁ MECÂNICA 04</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="B101" t="str">
-            <v>PC05</v>
-          </cell>
-          <cell r="C101" t="str">
-            <v>924 K 05</v>
-          </cell>
-          <cell r="D101" t="str">
-            <v>PÁ MECÂNICA 05</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="B102" t="str">
-            <v>GG04</v>
-          </cell>
-          <cell r="C102" t="str">
-            <v>GERADOR 04</v>
-          </cell>
-          <cell r="D102" t="str">
-            <v>GERADOR 04</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="B103" t="str">
-            <v>GG05</v>
-          </cell>
-          <cell r="C103" t="str">
-            <v>GERADOR 05</v>
-          </cell>
-          <cell r="D103" t="str">
-            <v>GERADOR PEQUENO 05</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="B104" t="str">
-            <v>GG06</v>
-          </cell>
-          <cell r="C104" t="str">
-            <v>GERADOR 06</v>
-          </cell>
-          <cell r="D104" t="str">
-            <v>GERADOR 06</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="B105" t="str">
-            <v>LC01</v>
-          </cell>
-          <cell r="C105" t="str">
-            <v>LIMPEZA-CAÇAMBAS</v>
-          </cell>
-          <cell r="D105" t="str">
-            <v>LIMPEZA DAS CAÇAMBAS</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="B106" t="str">
-            <v>GGMM</v>
-          </cell>
-          <cell r="C106" t="str">
-            <v>GG UA MM</v>
-          </cell>
-          <cell r="D106" t="str">
-            <v>GRUPO GERADOR USINA M. MONTE</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="B107" t="str">
-            <v>JBMM</v>
-          </cell>
-          <cell r="C107" t="str">
-            <v>JUMBO UA MM</v>
-          </cell>
-          <cell r="D107" t="str">
-            <v>JUMBO USINA M. MANTE</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="B108" t="str">
-            <v>PCMM</v>
-          </cell>
-          <cell r="C108" t="str">
-            <v>PC UA MM</v>
-          </cell>
-          <cell r="D108" t="str">
-            <v>PÁ CARREGADEIRA UA M. MONTE</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="B109"/>
-          <cell r="C109"/>
-          <cell r="D109"/>
-        </row>
-        <row r="110">
-          <cell r="B110"/>
-          <cell r="C110"/>
-          <cell r="D110"/>
-        </row>
-        <row r="111">
-          <cell r="B111"/>
-          <cell r="C111"/>
-          <cell r="D111"/>
-        </row>
-        <row r="112">
-          <cell r="B112" t="str">
-            <v>CM05</v>
-          </cell>
-          <cell r="C112" t="str">
-            <v>OHX2270</v>
-          </cell>
-          <cell r="D112" t="str">
-            <v>CAM. MELOSO CM 05</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="B113" t="str">
-            <v>CM04</v>
-          </cell>
-          <cell r="C113" t="str">
-            <v>PNX8017</v>
-          </cell>
-          <cell r="D113" t="str">
-            <v>CAM. MELOSO CM 04</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="B114" t="str">
-            <v>CA01</v>
-          </cell>
-          <cell r="C114" t="str">
-            <v>PNP5736</v>
-          </cell>
-          <cell r="D114" t="str">
-            <v>CAMINHÃO DE APOIO</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="B115" t="str">
-            <v>CP01</v>
-          </cell>
-          <cell r="C115" t="str">
-            <v>POA3579</v>
-          </cell>
-          <cell r="D115" t="str">
-            <v>CAMINHÃO PIPA</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="B116" t="str">
-            <v>VE01</v>
-          </cell>
-          <cell r="C116" t="str">
-            <v>HVV9901</v>
-          </cell>
-          <cell r="D116" t="str">
-            <v>VERANEIO</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="B117" t="str">
-            <v>TA01</v>
-          </cell>
-          <cell r="C117" t="str">
-            <v>IPJ8864</v>
-          </cell>
-          <cell r="D117" t="str">
-            <v>TANQUE P/ CAP 01</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="B118" t="str">
-            <v>MTQ01</v>
-          </cell>
-          <cell r="C118" t="str">
-            <v>M-IPJ8864</v>
-          </cell>
-          <cell r="D118" t="str">
-            <v>MAÇARICO TANQUE 01</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="B119" t="str">
-            <v>CTQ02</v>
-          </cell>
-          <cell r="C119" t="str">
-            <v>PMU3018</v>
-          </cell>
-          <cell r="D119" t="str">
-            <v>TANQUE P/ CAP 02</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="B120" t="str">
-            <v>M-TQ02</v>
-          </cell>
-          <cell r="C120" t="str">
-            <v>M-PMU3018</v>
-          </cell>
-          <cell r="D120" t="str">
-            <v>MAÇARICO TANQUE 02</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="B121" t="str">
-            <v>CT02</v>
-          </cell>
-          <cell r="C121" t="str">
-            <v>PMZ8670</v>
-          </cell>
-          <cell r="D121" t="str">
-            <v>TANQUE P/ CAP</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="B122" t="str">
-            <v>CT03</v>
-          </cell>
-          <cell r="C122" t="str">
-            <v>PNO7767</v>
-          </cell>
-          <cell r="D122" t="str">
-            <v>CARRETA COPA 03</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="B123" t="str">
-            <v>CP01</v>
-          </cell>
-          <cell r="C123" t="str">
-            <v>NVB8020</v>
-          </cell>
-          <cell r="D123" t="str">
-            <v>CAMINHÃO PLATAFORMA 01</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="B124" t="str">
-            <v>CP11</v>
-          </cell>
-          <cell r="C124" t="str">
-            <v>SBC1C59</v>
-          </cell>
-          <cell r="D124" t="str">
-            <v>CAMINHÃO PLATAFORMA TERC</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="B125" t="str">
-            <v>VC28</v>
-          </cell>
-          <cell r="C125" t="str">
-            <v>SBA6173</v>
-          </cell>
-          <cell r="D125" t="str">
-            <v>S-10</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="B126" t="str">
-            <v>M-01</v>
-          </cell>
-          <cell r="C126" t="str">
-            <v>MINERMAC</v>
-          </cell>
-          <cell r="D126" t="str">
-            <v>MINERMAC</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="B127" t="str">
-            <v>RE-01</v>
-          </cell>
-          <cell r="C127" t="str">
-            <v>RETRO 01</v>
-          </cell>
-          <cell r="D127" t="str">
-            <v>RETROESCAVADEIRA CASE</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="B128" t="str">
-            <v>EQ01</v>
-          </cell>
-          <cell r="C128" t="str">
-            <v>EH03</v>
-          </cell>
-          <cell r="D128" t="str">
-            <v>ESCAVADEIRA HIDRÁULICA CX220</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="B129" t="str">
-            <v>EQ02</v>
-          </cell>
-          <cell r="C129" t="str">
-            <v>MN06</v>
-          </cell>
-          <cell r="D129" t="str">
-            <v>MOTONIVELADORA MN06</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="B130" t="str">
-            <v>EQ03</v>
-          </cell>
-          <cell r="C130" t="str">
-            <v>RV04</v>
-          </cell>
-          <cell r="D130" t="str">
-            <v>ROLO COMACTADOR DYNAPAC</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="B131"/>
-          <cell r="C131"/>
-          <cell r="D131"/>
-        </row>
-        <row r="132">
-          <cell r="B132"/>
-          <cell r="C132"/>
-          <cell r="D132"/>
-        </row>
-        <row r="133">
-          <cell r="B133"/>
-          <cell r="C133"/>
-          <cell r="D133"/>
-        </row>
-        <row r="134">
-          <cell r="B134" t="str">
-            <v>PREFIXO</v>
-          </cell>
-          <cell r="C134"/>
-          <cell r="D134" t="str">
-            <v>EQUIPAMENTO</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="B135"/>
-          <cell r="C135"/>
-          <cell r="D135"/>
-        </row>
-        <row r="136">
-          <cell r="B136" t="str">
-            <v>VC06</v>
-          </cell>
-          <cell r="C136" t="str">
-            <v>POK1620</v>
-          </cell>
-          <cell r="D136" t="str">
-            <v>FOX</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="B137" t="str">
-            <v>VC14</v>
-          </cell>
-          <cell r="C137" t="str">
-            <v>PNZ2668</v>
-          </cell>
-          <cell r="D137" t="str">
-            <v>SAVEIRO</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="B138" t="str">
-            <v>VC21</v>
-          </cell>
-          <cell r="C138" t="str">
-            <v>PON4I92</v>
-          </cell>
-          <cell r="D138" t="str">
-            <v>GOL</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="B139" t="str">
-            <v>VC22</v>
-          </cell>
-          <cell r="C139" t="str">
-            <v>SAU8F49</v>
-          </cell>
-          <cell r="D139" t="str">
-            <v>SAVEIRO</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="B140" t="str">
-            <v>VC23</v>
-          </cell>
-          <cell r="C140" t="str">
-            <v>SBO3G34</v>
-          </cell>
-          <cell r="D140" t="str">
-            <v>ARGO</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="B141" t="str">
-            <v>VC24</v>
-          </cell>
-          <cell r="C141" t="str">
-            <v>RII2E47</v>
-          </cell>
-          <cell r="D141" t="str">
-            <v>PAJERO</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="B142" t="str">
-            <v>VC25</v>
-          </cell>
-          <cell r="C142" t="str">
-            <v>SIZ4J02</v>
-          </cell>
-          <cell r="D142" t="str">
-            <v>KWID</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="B143" t="str">
-            <v>VC26</v>
-          </cell>
-          <cell r="C143" t="str">
-            <v>PNC7863</v>
-          </cell>
-          <cell r="D143" t="str">
-            <v>FORDCAR</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="B144" t="str">
-            <v>VC27</v>
-          </cell>
-          <cell r="C144" t="str">
-            <v>SYZ2A26</v>
-          </cell>
-          <cell r="D144" t="str">
-            <v>FIAT MOBI</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="B145" t="str">
-            <v>VC27</v>
-          </cell>
-          <cell r="C145" t="str">
-            <v>SBB9F67</v>
-          </cell>
-          <cell r="D145" t="str">
-            <v>JEEP COMPAS</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="B146" t="str">
-            <v>VC28</v>
-          </cell>
-          <cell r="C146" t="str">
-            <v>SBA6I73</v>
-          </cell>
-          <cell r="D146" t="str">
-            <v>S-10</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="B147"/>
-          <cell r="C147"/>
-          <cell r="D147"/>
-        </row>
-        <row r="148">
-          <cell r="B148"/>
-          <cell r="C148"/>
-          <cell r="D148"/>
-        </row>
-        <row r="149">
-          <cell r="B149" t="str">
-            <v>VT03</v>
-          </cell>
-          <cell r="C149" t="str">
-            <v>OSD6B81</v>
-          </cell>
-          <cell r="D149" t="str">
-            <v>STRADA</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="B150" t="str">
-            <v>VT04</v>
-          </cell>
-          <cell r="C150" t="str">
-            <v>NVC8214</v>
-          </cell>
-          <cell r="D150" t="str">
-            <v>GOL</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="B151" t="str">
-            <v>VT05</v>
-          </cell>
-          <cell r="C151" t="str">
-            <v>AUT7H23</v>
-          </cell>
-          <cell r="D151" t="str">
-            <v>VOYAGE</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="B152" t="str">
-            <v>VT06</v>
-          </cell>
-          <cell r="C152" t="str">
-            <v>RIF2192</v>
-          </cell>
-          <cell r="D152" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="B153" t="str">
-            <v>VT08</v>
-          </cell>
-          <cell r="C153" t="str">
-            <v>OCN7B17</v>
-          </cell>
-          <cell r="D153" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="B154" t="str">
-            <v>VT09</v>
-          </cell>
-          <cell r="C154" t="str">
-            <v>KMA3G38</v>
-          </cell>
-          <cell r="D154" t="str">
-            <v>COROLA</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="B155" t="str">
-            <v>VT10</v>
-          </cell>
-          <cell r="C155" t="str">
-            <v>RIJ9E30</v>
-          </cell>
-          <cell r="D155" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="B156" t="str">
-            <v>VT11</v>
-          </cell>
-          <cell r="C156" t="str">
-            <v>SBO1A58</v>
-          </cell>
-          <cell r="D156" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="B157" t="str">
-            <v>VT12</v>
-          </cell>
-          <cell r="C157" t="str">
-            <v>HWW8389</v>
-          </cell>
-          <cell r="D157" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="B158" t="str">
-            <v>VT13</v>
-          </cell>
-          <cell r="C158" t="str">
-            <v>HXL5674</v>
-          </cell>
-          <cell r="D158" t="str">
-            <v>CELTA</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="B159" t="str">
-            <v>VT14</v>
-          </cell>
-          <cell r="C159" t="str">
-            <v>OSP5227</v>
-          </cell>
-          <cell r="D159" t="str">
-            <v>FOX</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="B160" t="str">
-            <v>VT15</v>
-          </cell>
-          <cell r="C160" t="str">
-            <v>MYY7536</v>
-          </cell>
-          <cell r="D160" t="str">
-            <v>PARATI</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="B161" t="str">
-            <v>VT16</v>
-          </cell>
-          <cell r="C161" t="str">
-            <v>SAR8B35</v>
-          </cell>
-          <cell r="D161" t="str">
-            <v>SAVEIRO</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="B162" t="str">
-            <v>VT17</v>
-          </cell>
-          <cell r="C162" t="str">
-            <v>OIC8768</v>
-          </cell>
-          <cell r="D162" t="str">
-            <v>CLASSIC</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="B163" t="str">
-            <v>VT18</v>
-          </cell>
-          <cell r="C163" t="str">
-            <v>PME4890</v>
-          </cell>
-          <cell r="D163" t="str">
-            <v>PALIO</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="B164" t="str">
-            <v>VT19</v>
-          </cell>
-          <cell r="C164" t="str">
-            <v>HVI3F83</v>
-          </cell>
-          <cell r="D164" t="str">
-            <v>CHEVETE</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="B165" t="str">
-            <v>VT20</v>
-          </cell>
-          <cell r="C165" t="str">
-            <v>ORP3H33</v>
-          </cell>
-          <cell r="D165" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="B166" t="str">
-            <v>VT21</v>
-          </cell>
-          <cell r="C166" t="str">
-            <v>NPV3A90</v>
-          </cell>
-          <cell r="D166" t="str">
-            <v>GOL</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="B167" t="str">
-            <v>VT22</v>
-          </cell>
-          <cell r="C167" t="str">
-            <v>KJM3D48</v>
-          </cell>
-          <cell r="D167" t="str">
-            <v>CELTA</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="B168" t="str">
-            <v>VT23</v>
-          </cell>
-          <cell r="C168" t="str">
-            <v>OCH1335</v>
-          </cell>
-          <cell r="D168" t="str">
-            <v>POLO</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="B169" t="str">
-            <v>VT24</v>
-          </cell>
-          <cell r="C169" t="str">
-            <v>NUT1D50</v>
-          </cell>
-          <cell r="D169" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="B170" t="str">
-            <v>VT25</v>
-          </cell>
-          <cell r="C170" t="str">
-            <v>NRE3F98</v>
-          </cell>
-          <cell r="D170" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="B171" t="str">
-            <v>VT26</v>
-          </cell>
-          <cell r="C171" t="str">
-            <v>HXS9281</v>
-          </cell>
-          <cell r="D171" t="str">
-            <v>GOL</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="B172" t="str">
-            <v>VT27</v>
-          </cell>
-          <cell r="C172" t="str">
-            <v>PBB8H75</v>
-          </cell>
-          <cell r="D172" t="str">
-            <v>GOL</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="B173" t="str">
-            <v>VT28</v>
-          </cell>
-          <cell r="C173" t="str">
-            <v>OIH9967</v>
-          </cell>
-          <cell r="D173" t="str">
-            <v>CELTA</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="B174" t="str">
-            <v>VT29</v>
-          </cell>
-          <cell r="C174" t="str">
-            <v>PMQ4A95</v>
-          </cell>
-          <cell r="D174" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="B175" t="str">
-            <v>VT30</v>
-          </cell>
-          <cell r="C175" t="str">
-            <v>NQZ9844</v>
-          </cell>
-          <cell r="D175" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="176">
-          <cell r="B176" t="str">
-            <v>VT31</v>
-          </cell>
-          <cell r="C176" t="str">
-            <v>EJL0247</v>
-          </cell>
-          <cell r="D176" t="str">
-            <v>CORSA</v>
-          </cell>
-        </row>
-        <row r="177">
-          <cell r="B177" t="str">
-            <v>VT32</v>
-          </cell>
-          <cell r="C177" t="str">
-            <v>ORO5993</v>
-          </cell>
-          <cell r="D177" t="str">
-            <v>HB20</v>
-          </cell>
-        </row>
-        <row r="178">
-          <cell r="B178" t="str">
-            <v>VT33</v>
-          </cell>
-          <cell r="C178" t="str">
-            <v>SBH0E69</v>
-          </cell>
-          <cell r="D178" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="179">
-          <cell r="B179" t="str">
-            <v>VT35</v>
-          </cell>
-          <cell r="C179" t="str">
-            <v>POG5674</v>
-          </cell>
-          <cell r="D179" t="str">
-            <v xml:space="preserve">MOTO </v>
-          </cell>
-        </row>
-        <row r="180">
-          <cell r="B180" t="str">
-            <v>VT34</v>
-          </cell>
-          <cell r="C180" t="str">
-            <v>ORR1929</v>
-          </cell>
-          <cell r="D180" t="str">
-            <v>VOYAGE</v>
-          </cell>
-        </row>
-        <row r="181">
-          <cell r="B181" t="str">
-            <v>VT34</v>
-          </cell>
-          <cell r="C181">
-            <v>0</v>
-          </cell>
-          <cell r="D181"/>
-        </row>
-        <row r="182">
-          <cell r="B182"/>
-          <cell r="C182"/>
-          <cell r="D182"/>
-        </row>
-        <row r="183">
-          <cell r="B183" t="str">
-            <v>DIV</v>
-          </cell>
-          <cell r="C183" t="str">
-            <v>DIVERSOS</v>
-          </cell>
-          <cell r="D183" t="str">
-            <v>LUBRIFICANTES, ETC</v>
-          </cell>
-        </row>
-        <row r="184">
-          <cell r="B184" t="str">
-            <v>EX LOB</v>
-          </cell>
-          <cell r="C184" t="str">
-            <v>EXTRAÇÃO LAB</v>
-          </cell>
-          <cell r="D184" t="str">
-            <v>ENSAIO LABORATORIO</v>
-          </cell>
-        </row>
-        <row r="185">
-          <cell r="B185" t="str">
-            <v>S. EXT 01</v>
-          </cell>
-          <cell r="C185" t="str">
-            <v>SONDA EXTRATORA</v>
-          </cell>
-          <cell r="D185" t="str">
-            <v>SONDA EXTRATORA 01</v>
-          </cell>
-        </row>
-        <row r="186">
-          <cell r="B186" t="str">
-            <v>DIV-T</v>
-          </cell>
-          <cell r="C186" t="str">
-            <v>DIV. TERCEIROS</v>
-          </cell>
-          <cell r="D186" t="str">
-            <v>LUBRIFICANTES, ETC</v>
-          </cell>
-        </row>
-        <row r="187">
-          <cell r="B187" t="str">
-            <v>L VA 01</v>
-          </cell>
-          <cell r="C187" t="str">
-            <v>L-VA CIBER</v>
-          </cell>
-          <cell r="D187" t="str">
-            <v>L.P/VA 01</v>
-          </cell>
-        </row>
-        <row r="188">
-          <cell r="B188" t="str">
-            <v>AGUA</v>
-          </cell>
-          <cell r="C188" t="str">
-            <v>L-VA LEE BOY</v>
-          </cell>
-          <cell r="D188" t="str">
-            <v>L.P/VA 04</v>
-          </cell>
-        </row>
-        <row r="189">
-          <cell r="B189" t="str">
-            <v>GELO</v>
-          </cell>
-          <cell r="C189" t="str">
-            <v>ÁGUA</v>
-          </cell>
-          <cell r="D189" t="str">
-            <v>GARRAFÃO 20L</v>
-          </cell>
-        </row>
-        <row r="190">
-          <cell r="B190" t="str">
-            <v>DISC TAC</v>
-          </cell>
-          <cell r="C190" t="str">
-            <v>GELO</v>
-          </cell>
-          <cell r="D190" t="str">
-            <v>GELO PCT 1 KG</v>
-          </cell>
-        </row>
-        <row r="191">
-          <cell r="B191" t="str">
-            <v>D.TAC</v>
-          </cell>
-          <cell r="C191" t="str">
-            <v>DISCO TACOGRAFO</v>
-          </cell>
-          <cell r="D191" t="str">
-            <v>DISCO TAC. 7 DIAS</v>
-          </cell>
-        </row>
-        <row r="192">
-          <cell r="B192" t="str">
-            <v xml:space="preserve">GÁS </v>
-          </cell>
-          <cell r="C192" t="str">
-            <v>AGUA DESMINERALIZADA</v>
-          </cell>
-          <cell r="D192" t="str">
-            <v>AGUA DESMINERALIZADA</v>
-          </cell>
-        </row>
-        <row r="193">
-          <cell r="B193" t="str">
-            <v>ADIT</v>
-          </cell>
-          <cell r="C193" t="str">
-            <v>GÁS DE COZINHA</v>
-          </cell>
-          <cell r="D193" t="str">
-            <v>GÁS P/ MAÇARICO USINA</v>
-          </cell>
-        </row>
-        <row r="194">
-          <cell r="B194" t="str">
-            <v>A-CB09</v>
-          </cell>
-          <cell r="C194" t="str">
-            <v>ADITIVO</v>
-          </cell>
-          <cell r="D194" t="str">
-            <v>ADITIVO P/ RADIADOR</v>
-          </cell>
-        </row>
-        <row r="195">
-          <cell r="B195" t="str">
-            <v>BET-01</v>
-          </cell>
-          <cell r="C195" t="str">
-            <v>BETONEIRA 01</v>
-          </cell>
-          <cell r="D195" t="str">
-            <v>BETONEIRA P/SERV. DRENAGEM NO IPU</v>
-          </cell>
-        </row>
-        <row r="196">
-          <cell r="B196" t="str">
-            <v>SAP 01</v>
-          </cell>
-          <cell r="C196" t="str">
-            <v>SAPINHO 01</v>
-          </cell>
-          <cell r="D196" t="str">
-            <v>SAPINHO P/SERV NO IPU</v>
-          </cell>
-        </row>
-        <row r="197">
-          <cell r="B197" t="str">
-            <v>A-CB09</v>
-          </cell>
-          <cell r="C197" t="str">
-            <v>A-OSG3B05</v>
-          </cell>
-          <cell r="D197" t="str">
-            <v>ARLA 32</v>
-          </cell>
-        </row>
-        <row r="198">
-          <cell r="B198" t="str">
-            <v>A-CB11</v>
-          </cell>
-          <cell r="C198" t="str">
-            <v>A-OZA3176</v>
-          </cell>
-          <cell r="D198" t="str">
-            <v>ARLA 32</v>
-          </cell>
-        </row>
-        <row r="199">
-          <cell r="B199" t="str">
-            <v>A-CB12</v>
-          </cell>
-          <cell r="C199" t="str">
-            <v>A-OSP9850</v>
-          </cell>
-          <cell r="D199" t="str">
-            <v>ARLA 32</v>
-          </cell>
-        </row>
-        <row r="200">
-          <cell r="B200" t="str">
-            <v>A-CB14</v>
-          </cell>
-          <cell r="C200" t="str">
-            <v>A-PNX5G67</v>
-          </cell>
-          <cell r="D200" t="str">
-            <v>ARLA 32</v>
-          </cell>
-        </row>
-        <row r="201">
-          <cell r="B201" t="str">
-            <v>A-CB18</v>
-          </cell>
-          <cell r="C201" t="str">
-            <v>A-PON7E59</v>
-          </cell>
-          <cell r="D201" t="str">
-            <v>ARLA 32</v>
-          </cell>
-        </row>
-        <row r="202">
-          <cell r="B202" t="str">
-            <v>A-CT03</v>
-          </cell>
-          <cell r="C202" t="str">
-            <v>A-SBP6D64</v>
-          </cell>
-          <cell r="D202" t="str">
-            <v>ARLA 32</v>
-          </cell>
-        </row>
-        <row r="203">
-          <cell r="B203" t="str">
-            <v>A-CB19</v>
-          </cell>
-          <cell r="C203" t="str">
-            <v>A-THT3E02</v>
-          </cell>
-          <cell r="D203" t="str">
-            <v>ARLA 32</v>
-          </cell>
-        </row>
-        <row r="204">
-          <cell r="B204" t="str">
-            <v>A-CT03</v>
-          </cell>
-          <cell r="C204" t="str">
-            <v>A-PNO7767</v>
-          </cell>
-          <cell r="D204" t="str">
-            <v>ARLA 32</v>
-          </cell>
-        </row>
-        <row r="205">
-          <cell r="B205" t="str">
-            <v>A-CE04</v>
-          </cell>
-          <cell r="C205" t="str">
-            <v>A-OSV2854</v>
-          </cell>
-          <cell r="D205" t="str">
-            <v>ARLA 32</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5894,10 +3606,6 @@
         <v>3</v>
       </c>
       <c r="D2" s="15"/>
-      <c r="E2" s="11" t="str">
-        <f>IFERROR(VLOOKUP($D$2,[3]CADASTRO!$B$9:L28,3,0),"")</f>
-        <v/>
-      </c>
       <c r="G2" s="17" t="s">
         <v>4</v>
       </c>
@@ -6380,10 +4088,7 @@
       <c r="K37" s="85"/>
     </row>
     <row r="38" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="E38" s="107" t="e">
-        <f>VLOOKUP(E37,[3]CADASTRO!$B$9:$D$447,3,0)</f>
-        <v>#N/A</v>
-      </c>
+      <c r="E38" s="107"/>
       <c r="F38" s="108"/>
       <c r="H38" s="84"/>
       <c r="K38" s="85"/>

--- a/template_posto.xlsx
+++ b/template_posto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moise\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA568BD-8870-49F0-B6C2-39F10BB00BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C222BC38-D87F-4D11-B0F5-B470B2268E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F2E926A6-1D7B-46C1-853C-913B9CD95B80}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E94F5EE3-E969-41F1-85BF-E3275F66CC13}"/>
   </bookViews>
   <sheets>
     <sheet name="PADRÃO" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,17 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="\a">#REF!</definedName>
     <definedName name="\b">#REF!</definedName>
     <definedName name="\p">#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PADRÃO!$A$7:$M$24</definedName>
-    <definedName name="A">[1]DIVERSOS!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">PADRÃO!$A$1:$M$23</definedName>
-    <definedName name="CACAMBA">'[2]CADASTRO DE CACAMBA'!$A$7:$AG$30</definedName>
-    <definedName name="SSS">[1]DIVERSOS!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PADRÃO!$A$6:$M$41</definedName>
+    <definedName name="A">[2]DIVERSOS!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">PADRÃO!$A$1:$M$40</definedName>
+    <definedName name="CACAMBA">'[3]CADASTRO DE CACAMBA'!$A$7:$AG$30</definedName>
+    <definedName name="SSS">[2]DIVERSOS!#REF!</definedName>
     <definedName name="wrn.Orçamento." hidden="1">{#N/A,#N/A,FALSE,"Planilha";#N/A,#N/A,FALSE,"Resumo";#N/A,#N/A,FALSE,"Fisico";#N/A,#N/A,FALSE,"Financeiro";#N/A,#N/A,FALSE,"Financeiro"}</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>OBRA:</t>
   </si>
@@ -62,13 +63,7 @@
     <t>RAZÃO SOCIAL</t>
   </si>
   <si>
-    <t>PIX</t>
-  </si>
-  <si>
     <t>DESCRIÇÃO:</t>
-  </si>
-  <si>
-    <t>PREÇO GASOLINA (L)</t>
   </si>
   <si>
     <t>AGÊNCIA:</t>
@@ -78,9 +73,6 @@
   </si>
   <si>
     <t>PERÍODO:</t>
-  </si>
-  <si>
-    <t>PREÇO DIESEL (L)</t>
   </si>
   <si>
     <t>CONTA:</t>
@@ -157,6 +149,9 @@
   <si>
     <t>ÁGUA</t>
   </si>
+  <si>
+    <t>PIX:</t>
+  </si>
 </sst>
 </file>
 
@@ -173,7 +168,7 @@
     <numFmt numFmtId="169" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,20 +208,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -756,7 +737,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -782,9 +763,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -809,7 +787,7 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -833,13 +811,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -857,15 +838,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -890,76 +877,79 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="7" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -968,7 +958,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -977,34 +967,34 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="2" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="9" fillId="2" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="9" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1013,7 +1003,7 @@
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1031,6 +1021,18 @@
     <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1055,31 +1057,7 @@
     <xf numFmtId="43" fontId="2" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1087,7 +1065,7 @@
     <cellStyle name="Moeda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
-    <cellStyle name="Vírgula 3 2" xfId="3" xr:uid="{D63D95D0-994E-47FB-91A6-43F071D8CF28}"/>
+    <cellStyle name="Vírgula 3 2" xfId="3" xr:uid="{69189CBC-1BB2-4261-8F3F-5C00F7C2B7FD}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1122,7 +1100,7 @@
         <xdr:cNvPr id="2" name="Picture 1785">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{427C4631-7022-4D26-A76F-1D4C3764739E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3697626D-0DF6-47C9-8ACA-CE5C40A75D16}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1160,6 +1138,100 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="PADRÃO"/>
+      <sheetName val="FLUXO DE EDIÇÃO"/>
+      <sheetName val="FORNECEDORES"/>
+      <sheetName val="CADASTRO"/>
+      <sheetName val="AGUIAR"/>
+      <sheetName val="MARV"/>
+      <sheetName val="RESUMOS --&gt;"/>
+      <sheetName val="RES. GERAL"/>
+      <sheetName val="TQ01"/>
+      <sheetName val="TQ03"/>
+      <sheetName val="TQ04"/>
+      <sheetName val="100C"/>
+      <sheetName val="RTN"/>
+      <sheetName val="SERV"/>
+      <sheetName val="RZD"/>
+      <sheetName val="BOA"/>
+      <sheetName val="JAG"/>
+      <sheetName val="BETUME"/>
+      <sheetName val="TCM04"/>
+      <sheetName val="PRODUÇÃO"/>
+      <sheetName val="TB PROD-OUT-23"/>
+      <sheetName val="CB`S COPA"/>
+      <sheetName val="DIVERSOS"/>
+      <sheetName val="ASFALTO"/>
+      <sheetName val="FINANCEIRO"/>
+      <sheetName val="CAÇ COPA --&gt;"/>
+      <sheetName val="CB11"/>
+      <sheetName val="CB12"/>
+      <sheetName val="CB13"/>
+      <sheetName val="CB15"/>
+      <sheetName val="CB16"/>
+      <sheetName val="CB18"/>
+      <sheetName val="CB19"/>
+      <sheetName val="CT03"/>
+      <sheetName val="CAÇ TERCEIROS)"/>
+      <sheetName val="CB23"/>
+      <sheetName val="CB24"/>
+      <sheetName val="CB25"/>
+      <sheetName val="CB29"/>
+      <sheetName val="CB30"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1229,7 +1301,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3552,30 +3624,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39819352-1957-4255-8F03-32A80EC18B32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53A95896-6778-41B0-9157-CFB10AA51555}">
   <sheetPr codeName="Planilha11">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:U120"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.21875" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="16" style="11" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="16" style="10" customWidth="1"/>
     <col min="4" max="4" width="15.21875" style="33" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="11" customWidth="1"/>
-    <col min="6" max="6" width="28.21875" style="16" customWidth="1"/>
-    <col min="7" max="7" width="18.88671875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" style="16" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" style="36" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" style="36" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" style="36" customWidth="1"/>
-    <col min="12" max="12" width="14.77734375" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.77734375" style="11" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="11" customWidth="1"/>
-    <col min="15" max="20" width="9.21875" style="11"/>
-    <col min="21" max="21" width="10.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.21875" style="11"/>
+    <col min="5" max="5" width="15.5546875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="28.21875" style="15" customWidth="1"/>
+    <col min="7" max="7" width="18.88671875" style="15" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" style="15" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" style="34" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" style="34" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" style="34" customWidth="1"/>
+    <col min="12" max="12" width="14.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.77734375" style="10" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="10" customWidth="1"/>
+    <col min="15" max="20" width="9.21875" style="10"/>
+    <col min="21" max="21" width="10.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.21875" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -3594,835 +3666,1216 @@
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="6"/>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="107" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="10"/>
-    </row>
-    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="G2" s="17" t="s">
+      <c r="J2" s="15"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19" t="s">
+      <c r="M2" s="21"/>
+    </row>
+    <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="16"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" s="22"/>
-    </row>
-    <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
       <c r="F3" s="26"/>
-      <c r="G3" s="27" t="s">
-        <v>8</v>
-      </c>
+      <c r="G3" s="27"/>
       <c r="H3" s="28"/>
       <c r="I3" s="29" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
       <c r="L3" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="32"/>
+    </row>
+    <row r="4" spans="1:13" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="38"/>
+    </row>
+    <row r="5" spans="1:13" ht="9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+    </row>
+    <row r="6" spans="1:13" s="46" customFormat="1" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="32"/>
-    </row>
-    <row r="4" spans="1:13" ht="9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-    </row>
-    <row r="5" spans="1:13" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="101" t="s">
+      <c r="C6" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="104"/>
-    </row>
-    <row r="6" spans="1:13" ht="9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
-    </row>
-    <row r="7" spans="1:13" s="44" customFormat="1" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="D6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="E6" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="F6" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="G6" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="H6" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="I6" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="J6" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="K6" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="42" t="s">
+      <c r="L6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="42" t="s">
+      <c r="M6" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" s="43" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="45"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="54" t="str">
-        <f>IF(J8="","",I8*J8)</f>
+    </row>
+    <row r="7" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="47"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="56" t="str">
+        <f>IF(J7="","",I7*J7)</f>
         <v/>
       </c>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-    </row>
-    <row r="9" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="54" t="str">
-        <f t="shared" ref="K9:K11" si="0">IF(J9="","",I9*J9)</f>
+      <c r="L7" s="57"/>
+      <c r="M7" s="58"/>
+    </row>
+    <row r="8" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="58"/>
+    </row>
+    <row r="9" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="47"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="58"/>
+    </row>
+    <row r="10" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="47"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="58"/>
+    </row>
+    <row r="11" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="47"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="58"/>
+    </row>
+    <row r="12" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="47"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="58"/>
+    </row>
+    <row r="13" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="58"/>
+    </row>
+    <row r="14" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="47"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="58"/>
+    </row>
+    <row r="15" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="47"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="58"/>
+    </row>
+    <row r="16" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="58"/>
+    </row>
+    <row r="17" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="47"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="56"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="58"/>
+    </row>
+    <row r="18" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="58"/>
+    </row>
+    <row r="19" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="47"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="56" t="str">
+        <f t="shared" ref="K19:K21" si="0">IF(J19="","",I19*J19)</f>
         <v/>
       </c>
-      <c r="L9" s="55"/>
-      <c r="M9" s="56"/>
-    </row>
-    <row r="10" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="54" t="str">
+      <c r="L19" s="57"/>
+      <c r="M19" s="58"/>
+    </row>
+    <row r="20" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="47"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="56" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L10" s="55"/>
-      <c r="M10" s="56"/>
-    </row>
-    <row r="11" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="45"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="54" t="str">
+      <c r="L20" s="57"/>
+      <c r="M20" s="58"/>
+    </row>
+    <row r="21" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="47"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="56" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L11" s="55"/>
-      <c r="M11" s="56"/>
-    </row>
-    <row r="12" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="45"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="54" t="str">
-        <f>IF(J12="","",I12*J12)</f>
+      <c r="L21" s="57"/>
+      <c r="M21" s="58"/>
+    </row>
+    <row r="22" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="47"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="58"/>
+    </row>
+    <row r="23" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="58"/>
+    </row>
+    <row r="24" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="47"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="58"/>
+    </row>
+    <row r="25" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="47"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="58"/>
+    </row>
+    <row r="26" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="47"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="58"/>
+    </row>
+    <row r="27" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="47"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="55"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="58"/>
+    </row>
+    <row r="28" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="47"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="58"/>
+    </row>
+    <row r="29" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="47"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="56" t="str">
+        <f>IF(J29="","",I29*J29)</f>
         <v/>
       </c>
-      <c r="L12" s="55"/>
-      <c r="M12" s="56"/>
-    </row>
-    <row r="13" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="54" t="str">
-        <f t="shared" ref="K13:K20" si="1">IF(J13="","",I13*J13)</f>
+      <c r="L29" s="57"/>
+      <c r="M29" s="58"/>
+    </row>
+    <row r="30" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="47"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="56" t="str">
+        <f t="shared" ref="K30:K38" si="1">IF(J30="","",I30*J30)</f>
         <v/>
       </c>
-      <c r="L13" s="55"/>
-      <c r="M13" s="56"/>
-    </row>
-    <row r="14" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="45"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="54" t="str">
+      <c r="L30" s="57"/>
+      <c r="M30" s="58"/>
+    </row>
+    <row r="31" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="47"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="56" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L14" s="61"/>
-      <c r="M14" s="56"/>
-    </row>
-    <row r="15" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="45"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="54" t="str">
+      <c r="L31" s="63"/>
+      <c r="M31" s="58"/>
+    </row>
+    <row r="32" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="47"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="56" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L15" s="61"/>
-      <c r="M15" s="56"/>
-    </row>
-    <row r="16" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="45"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="53"/>
-      <c r="K16" s="54" t="str">
+      <c r="L32" s="63"/>
+      <c r="M32" s="58"/>
+    </row>
+    <row r="33" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="47"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="56" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L16" s="61"/>
-      <c r="M16" s="56"/>
-    </row>
-    <row r="17" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="45"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="54" t="str">
+      <c r="L33" s="63"/>
+      <c r="M33" s="58"/>
+    </row>
+    <row r="34" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="47"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="56" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L17" s="61"/>
-      <c r="M17" s="56"/>
-    </row>
-    <row r="18" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="54" t="str">
+      <c r="L34" s="63"/>
+      <c r="M34" s="58"/>
+    </row>
+    <row r="35" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="47"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="56" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L18" s="61"/>
-      <c r="M18" s="56"/>
-    </row>
-    <row r="19" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="45"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="54" t="str">
+      <c r="L35" s="63"/>
+      <c r="M35" s="58"/>
+    </row>
+    <row r="36" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="47"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="62"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="56" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L19" s="61"/>
-      <c r="M19" s="56"/>
-    </row>
-    <row r="20" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="45"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="54" t="str">
+      <c r="L36" s="63"/>
+      <c r="M36" s="58"/>
+    </row>
+    <row r="37" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="47"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="62"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="56" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L20" s="61"/>
-      <c r="M20" s="56"/>
-    </row>
-    <row r="21" spans="1:13" s="57" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="62"/>
-      <c r="B21" s="63"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="67"/>
-      <c r="M21" s="68"/>
-    </row>
-    <row r="22" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="69"/>
-      <c r="B22" s="70"/>
-      <c r="C22" s="71" t="s">
+      <c r="L37" s="63"/>
+      <c r="M37" s="58"/>
+    </row>
+    <row r="38" spans="1:13" s="59" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="64"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="56" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L38" s="70"/>
+      <c r="M38" s="71"/>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="72"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="75"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="77">
+        <f>SUBTOTAL(9,I7:I38)</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="78"/>
+      <c r="K39" s="79">
+        <f>SUBTOTAL(9,K7:K38)</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" s="81"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="82"/>
+      <c r="I40" s="83"/>
+      <c r="J40" s="84"/>
+      <c r="K40" s="85"/>
+      <c r="L40" s="86"/>
+      <c r="M40" s="81"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H41" s="87"/>
+      <c r="K41" s="88"/>
+      <c r="M41" s="89"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D42" s="10"/>
+      <c r="H42" s="87"/>
+      <c r="K42" s="88"/>
+      <c r="M42" s="90"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D43" s="10"/>
+      <c r="H43" s="87"/>
+      <c r="K43" s="88"/>
+      <c r="M43" s="90"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H44" s="87"/>
+      <c r="K44" s="88"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H45" s="87"/>
+      <c r="K45" s="88"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H46" s="87"/>
+      <c r="K46" s="88"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H47" s="87"/>
+      <c r="K47" s="88"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H48" s="87"/>
+      <c r="K48" s="88"/>
+    </row>
+    <row r="49" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="H49" s="87"/>
+      <c r="K49" s="88"/>
+    </row>
+    <row r="50" spans="4:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H50" s="87"/>
+      <c r="I50" s="91" t="s">
+        <v>23</v>
+      </c>
+      <c r="J50" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" s="93">
+        <f>SUMIFS($K$7:K45,$H$7:H45,J50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H51" s="87"/>
+      <c r="I51" s="94"/>
+      <c r="J51" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="72"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="74">
-        <f>SUBTOTAL(9,I8:I21)</f>
+      <c r="K51" s="93">
+        <f>SUMIFS(K7:K45,H7:H45,J51)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="75"/>
-      <c r="K22" s="76">
-        <f>SUBTOTAL(9,K8:K21)</f>
+    </row>
+    <row r="52" spans="4:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H52" s="87"/>
+      <c r="I52" s="94"/>
+      <c r="J52" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="K52" s="94"/>
+    </row>
+    <row r="53" spans="4:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H53" s="87"/>
+      <c r="K53" s="88"/>
+    </row>
+    <row r="54" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="E54" s="95"/>
+      <c r="F54" s="96"/>
+      <c r="H54" s="87"/>
+      <c r="K54" s="88"/>
+    </row>
+    <row r="55" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="E55" s="97"/>
+      <c r="F55" s="98"/>
+      <c r="H55" s="87"/>
+      <c r="K55" s="88"/>
+    </row>
+    <row r="56" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="E56" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56" s="100" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="87"/>
+      <c r="K56" s="88"/>
+    </row>
+    <row r="57" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D57" s="101" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="102">
+        <f>SUMIFS($I$7:$I$45,$H$7:$H$45,$D57,$G$7:$G$45,E$54)</f>
         <v>0</v>
       </c>
-      <c r="L22" s="77" t="s">
-        <v>25</v>
-      </c>
-      <c r="M22" s="78"/>
-    </row>
-    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="79"/>
-      <c r="I23" s="80"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="82"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="78"/>
-    </row>
-    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H24" s="84"/>
-      <c r="K24" s="85"/>
-      <c r="M24" s="86"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D25" s="11"/>
-      <c r="H25" s="84"/>
-      <c r="K25" s="85"/>
-      <c r="M25" s="87"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D26" s="11"/>
-      <c r="H26" s="84"/>
-      <c r="K26" s="85"/>
-      <c r="M26" s="87"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H27" s="84"/>
-      <c r="K27" s="85"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H28" s="84"/>
-      <c r="K28" s="85"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H29" s="84"/>
-      <c r="K29" s="85"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H30" s="84"/>
-      <c r="K30" s="85"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H31" s="84"/>
-      <c r="K31" s="85"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H32" s="84"/>
-      <c r="K32" s="85"/>
-    </row>
-    <row r="33" spans="4:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="H33" s="84"/>
-      <c r="I33" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="K33" s="90">
-        <f>SUMIFS($K$8:K28,$H$8:H28,J33)</f>
+      <c r="F57" s="103">
+        <f>SUMIFS($K$7:$K$45,$H$7:$H$45,$D57,$G$7:$G$45,E$54)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="4:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="H34" s="84"/>
-      <c r="I34" s="91"/>
-      <c r="J34" s="89" t="s">
+      <c r="H57" s="87"/>
+      <c r="K57" s="88"/>
+    </row>
+    <row r="58" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D58" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="102">
+        <f>SUMIFS($I$7:$I$45,$H$7:$H$45,$D58,$G$7:$G$45,E$54)</f>
+        <v>0</v>
+      </c>
+      <c r="F58" s="103">
+        <f>SUMIFS($K$7:$K$45,$H$7:$H$45,$D58,$G$7:$G$45,E$54)</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="87"/>
+      <c r="K58" s="88"/>
+    </row>
+    <row r="59" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D59" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="K34" s="90">
-        <f>SUMIFS(K8:K28,H8:H28,J34)</f>
+      <c r="E59" s="102">
+        <f>SUMIFS($I$7:$I$45,$H$7:$H$45,$D59,$G$7:$G$45,E$54)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="4:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="H35" s="84"/>
-      <c r="I35" s="91"/>
-      <c r="J35" s="89" t="s">
+      <c r="F59" s="103">
+        <f>SUMIFS($K$7:$K$45,$H$7:$H$45,$D59,$G$7:$G$45,E$54)</f>
+        <v>0</v>
+      </c>
+      <c r="H59" s="87"/>
+      <c r="J59" s="104"/>
+      <c r="K59" s="88"/>
+    </row>
+    <row r="60" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D60" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="K35" s="91"/>
-    </row>
-    <row r="36" spans="4:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H36" s="84"/>
-      <c r="K36" s="85"/>
-    </row>
-    <row r="37" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="E37" s="105">
-        <f>D2</f>
+      <c r="E60" s="102">
+        <f>SUMIFS($I$7:$I$45,$H$7:$H$45,$D60,$G$7:$G$45,E$54)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="106"/>
-      <c r="H37" s="84"/>
-      <c r="K37" s="85"/>
-    </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="E38" s="107"/>
-      <c r="F38" s="108"/>
-      <c r="H38" s="84"/>
-      <c r="K38" s="85"/>
-    </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="E39" s="92" t="s">
+      <c r="F60" s="103">
+        <f>SUMIFS($K$7:$K$45,$H$7:$H$45,$D60,$G$7:$G$45,E$54)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="87"/>
+      <c r="K60" s="88"/>
+    </row>
+    <row r="61" spans="4:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D61" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="F39" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="H39" s="84"/>
-      <c r="K39" s="85"/>
-    </row>
-    <row r="40" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D40" s="94" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" s="95">
-        <f>SUMIFS($I$8:$I$28,$H$8:$H$28,$D40,$G$8:$G$28,E$37)</f>
+      <c r="E61" s="102">
+        <f>SUMIFS($I$7:$I$45,$H$7:$H$45,$D61,$G$7:$G$45,E$54)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="96">
-        <f>SUMIFS($K$8:$K$28,$H$8:$H$28,$D40,$G$8:$G$28,E$37)</f>
+      <c r="F61" s="103">
+        <f>SUMIFS($K$7:$K$45,$H$7:$H$45,$D61,$G$7:$G$45,E$54)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="84"/>
-      <c r="K40" s="85"/>
-    </row>
-    <row r="41" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D41" s="94" t="s">
-        <v>27</v>
-      </c>
-      <c r="E41" s="95">
-        <f>SUMIFS($I$8:$I$28,$H$8:$H$28,$D41,$G$8:$G$28,E$37)</f>
+      <c r="H61" s="87"/>
+      <c r="K61" s="88"/>
+    </row>
+    <row r="62" spans="4:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E62" s="105">
+        <f>SUBTOTAL(9,E57:E61)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="96">
-        <f>SUMIFS($K$8:$K$28,$H$8:$H$28,$D41,$G$8:$G$28,E$37)</f>
+      <c r="F62" s="106">
+        <f>SUM(F57:F61)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="84"/>
-      <c r="K41" s="85"/>
-    </row>
-    <row r="42" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D42" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="E42" s="95">
-        <f>SUMIFS($I$8:$I$28,$H$8:$H$28,$D42,$G$8:$G$28,E$37)</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="96">
-        <f>SUMIFS($K$8:$K$28,$H$8:$H$28,$D42,$G$8:$G$28,E$37)</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="84"/>
-      <c r="J42" s="97"/>
-      <c r="K42" s="85"/>
-    </row>
-    <row r="43" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D43" s="94" t="s">
-        <v>32</v>
-      </c>
-      <c r="E43" s="95">
-        <f>SUMIFS($I$8:$I$28,$H$8:$H$28,$D43,$G$8:$G$28,E$37)</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="96">
-        <f>SUMIFS($K$8:$K$28,$H$8:$H$28,$D43,$G$8:$G$28,E$37)</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="84"/>
-      <c r="K43" s="85"/>
-    </row>
-    <row r="44" spans="4:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D44" s="94" t="s">
-        <v>33</v>
-      </c>
-      <c r="E44" s="95">
-        <f>SUMIFS($I$8:$I$28,$H$8:$H$28,$D44,$G$8:$G$28,E$37)</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="96">
-        <f>SUMIFS($K$8:$K$28,$H$8:$H$28,$D44,$G$8:$G$28,E$37)</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="84"/>
-      <c r="K44" s="85"/>
-    </row>
-    <row r="45" spans="4:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E45" s="98">
-        <f>SUBTOTAL(9,E40:E44)</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="99">
-        <f>SUM(F40:F44)</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="84"/>
-      <c r="K45" s="85"/>
-    </row>
-    <row r="46" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="H46" s="84"/>
-      <c r="K46" s="85"/>
-    </row>
-    <row r="47" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="H47" s="84"/>
-      <c r="K47" s="85"/>
-    </row>
-    <row r="48" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="H48" s="84"/>
-      <c r="K48" s="85"/>
-    </row>
-    <row r="49" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H49" s="84"/>
-      <c r="K49" s="85"/>
-    </row>
-    <row r="50" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H50" s="84"/>
-      <c r="K50" s="85"/>
-    </row>
-    <row r="51" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H51" s="84"/>
-      <c r="K51" s="85"/>
-    </row>
-    <row r="52" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H52" s="84"/>
-      <c r="K52" s="85"/>
-    </row>
-    <row r="53" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H53" s="84"/>
-      <c r="K53" s="85"/>
-    </row>
-    <row r="54" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H54" s="84"/>
-      <c r="K54" s="85"/>
-    </row>
-    <row r="55" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H55" s="84"/>
-      <c r="K55" s="85"/>
-    </row>
-    <row r="56" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H56" s="84"/>
-      <c r="K56" s="85"/>
-    </row>
-    <row r="57" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H57" s="84"/>
-      <c r="K57" s="85"/>
-    </row>
-    <row r="58" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H58" s="84"/>
-      <c r="K58" s="85"/>
-    </row>
-    <row r="59" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H59" s="84"/>
-      <c r="K59" s="85"/>
-    </row>
-    <row r="60" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H60" s="84"/>
-      <c r="K60" s="85"/>
-    </row>
-    <row r="61" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H61" s="84"/>
-      <c r="K61" s="85"/>
-    </row>
-    <row r="62" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H62" s="84"/>
-      <c r="K62" s="85"/>
-    </row>
-    <row r="63" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H63" s="84"/>
-      <c r="K63" s="85"/>
-    </row>
-    <row r="64" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H64" s="84"/>
-      <c r="K64" s="85"/>
+      <c r="H62" s="87"/>
+      <c r="K62" s="88"/>
+    </row>
+    <row r="63" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="H63" s="87"/>
+      <c r="K63" s="88"/>
+    </row>
+    <row r="64" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="H64" s="87"/>
+      <c r="K64" s="88"/>
     </row>
     <row r="65" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H65" s="84"/>
-      <c r="K65" s="85"/>
+      <c r="H65" s="87"/>
+      <c r="K65" s="88"/>
     </row>
     <row r="66" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H66" s="84"/>
-      <c r="K66" s="85"/>
+      <c r="H66" s="87"/>
+      <c r="K66" s="88"/>
     </row>
     <row r="67" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H67" s="84"/>
-      <c r="K67" s="85"/>
+      <c r="H67" s="87"/>
+      <c r="K67" s="88"/>
     </row>
     <row r="68" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H68" s="84"/>
-      <c r="K68" s="85"/>
+      <c r="H68" s="87"/>
+      <c r="K68" s="88"/>
     </row>
     <row r="69" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H69" s="84"/>
-      <c r="K69" s="85"/>
+      <c r="H69" s="87"/>
+      <c r="K69" s="88"/>
     </row>
     <row r="70" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H70" s="84"/>
-      <c r="K70" s="85"/>
+      <c r="H70" s="87"/>
+      <c r="K70" s="88"/>
     </row>
     <row r="71" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H71" s="84"/>
-      <c r="K71" s="85"/>
+      <c r="H71" s="87"/>
+      <c r="K71" s="88"/>
     </row>
     <row r="72" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H72" s="84"/>
-      <c r="K72" s="85"/>
+      <c r="H72" s="87"/>
+      <c r="K72" s="88"/>
     </row>
     <row r="73" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H73" s="84"/>
-      <c r="K73" s="85"/>
+      <c r="H73" s="87"/>
+      <c r="K73" s="88"/>
     </row>
     <row r="74" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H74" s="84"/>
-      <c r="K74" s="85"/>
+      <c r="H74" s="87"/>
+      <c r="K74" s="88"/>
     </row>
     <row r="75" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H75" s="84"/>
-      <c r="K75" s="85"/>
+      <c r="H75" s="87"/>
+      <c r="K75" s="88"/>
     </row>
     <row r="76" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H76" s="84"/>
-      <c r="K76" s="85"/>
+      <c r="H76" s="87"/>
+      <c r="K76" s="88"/>
     </row>
     <row r="77" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H77" s="84"/>
-      <c r="K77" s="85"/>
+      <c r="H77" s="87"/>
+      <c r="K77" s="88"/>
     </row>
     <row r="78" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H78" s="84"/>
-      <c r="K78" s="85"/>
+      <c r="H78" s="87"/>
+      <c r="K78" s="88"/>
     </row>
     <row r="79" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H79" s="84"/>
-      <c r="K79" s="85"/>
+      <c r="H79" s="87"/>
+      <c r="K79" s="88"/>
     </row>
     <row r="80" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H80" s="84"/>
-      <c r="K80" s="85"/>
+      <c r="H80" s="87"/>
+      <c r="K80" s="88"/>
     </row>
     <row r="81" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H81" s="84"/>
-      <c r="K81" s="85"/>
+      <c r="H81" s="87"/>
+      <c r="K81" s="88"/>
     </row>
     <row r="82" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H82" s="84"/>
-      <c r="K82" s="85"/>
+      <c r="H82" s="87"/>
+      <c r="K82" s="88"/>
     </row>
     <row r="83" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H83" s="84"/>
-      <c r="K83" s="85"/>
+      <c r="H83" s="87"/>
+      <c r="K83" s="88"/>
     </row>
     <row r="84" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H84" s="84"/>
-      <c r="K84" s="85"/>
+      <c r="H84" s="87"/>
+      <c r="K84" s="88"/>
     </row>
     <row r="85" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H85" s="84"/>
-      <c r="K85" s="85"/>
+      <c r="H85" s="87"/>
+      <c r="K85" s="88"/>
     </row>
     <row r="86" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H86" s="84"/>
-      <c r="K86" s="85"/>
+      <c r="H86" s="87"/>
+      <c r="K86" s="88"/>
     </row>
     <row r="87" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H87" s="84"/>
-      <c r="K87" s="85"/>
+      <c r="H87" s="87"/>
+      <c r="K87" s="88"/>
     </row>
     <row r="88" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H88" s="84"/>
-      <c r="K88" s="85"/>
+      <c r="H88" s="87"/>
+      <c r="K88" s="88"/>
     </row>
     <row r="89" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H89" s="84"/>
+      <c r="H89" s="87"/>
+      <c r="K89" s="88"/>
     </row>
     <row r="90" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H90" s="84"/>
+      <c r="H90" s="87"/>
+      <c r="K90" s="88"/>
     </row>
     <row r="91" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H91" s="84"/>
+      <c r="H91" s="87"/>
+      <c r="K91" s="88"/>
     </row>
     <row r="92" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H92" s="84"/>
+      <c r="H92" s="87"/>
+      <c r="K92" s="88"/>
     </row>
     <row r="93" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H93" s="84"/>
+      <c r="H93" s="87"/>
+      <c r="K93" s="88"/>
     </row>
     <row r="94" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H94" s="84"/>
+      <c r="H94" s="87"/>
+      <c r="K94" s="88"/>
     </row>
     <row r="95" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H95" s="84"/>
+      <c r="H95" s="87"/>
+      <c r="K95" s="88"/>
     </row>
     <row r="96" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H96" s="84"/>
-    </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H97" s="84"/>
-    </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H98" s="84"/>
-    </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H99" s="84"/>
-    </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H100" s="84"/>
-    </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H101" s="84"/>
-    </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H102" s="84"/>
-    </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H103" s="84"/>
+      <c r="H96" s="87"/>
+      <c r="K96" s="88"/>
+    </row>
+    <row r="97" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H97" s="87"/>
+      <c r="K97" s="88"/>
+    </row>
+    <row r="98" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H98" s="87"/>
+      <c r="K98" s="88"/>
+    </row>
+    <row r="99" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H99" s="87"/>
+      <c r="K99" s="88"/>
+    </row>
+    <row r="100" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H100" s="87"/>
+      <c r="K100" s="88"/>
+    </row>
+    <row r="101" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H101" s="87"/>
+      <c r="K101" s="88"/>
+    </row>
+    <row r="102" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H102" s="87"/>
+      <c r="K102" s="88"/>
+    </row>
+    <row r="103" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H103" s="87"/>
+      <c r="K103" s="88"/>
+    </row>
+    <row r="104" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H104" s="87"/>
+      <c r="K104" s="88"/>
+    </row>
+    <row r="105" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H105" s="87"/>
+      <c r="K105" s="88"/>
+    </row>
+    <row r="106" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H106" s="87"/>
+    </row>
+    <row r="107" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H107" s="87"/>
+    </row>
+    <row r="108" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H108" s="87"/>
+    </row>
+    <row r="109" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H109" s="87"/>
+    </row>
+    <row r="110" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H110" s="87"/>
+    </row>
+    <row r="111" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H111" s="87"/>
+    </row>
+    <row r="112" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H112" s="87"/>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H113" s="87"/>
+    </row>
+    <row r="114" spans="1:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="33"/>
+      <c r="B114" s="10"/>
+      <c r="C114" s="10"/>
+      <c r="D114" s="33"/>
+      <c r="E114" s="10"/>
+      <c r="F114" s="15"/>
+      <c r="G114" s="15"/>
+      <c r="H114" s="87"/>
+      <c r="L114" s="10"/>
+      <c r="M114" s="10"/>
+      <c r="N114" s="10"/>
+      <c r="O114" s="10"/>
+      <c r="P114" s="10"/>
+      <c r="Q114" s="10"/>
+      <c r="R114" s="10"/>
+      <c r="S114" s="10"/>
+      <c r="T114" s="10"/>
+      <c r="U114" s="10"/>
+    </row>
+    <row r="115" spans="1:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="33"/>
+      <c r="B115" s="10"/>
+      <c r="C115" s="10"/>
+      <c r="D115" s="33"/>
+      <c r="E115" s="10"/>
+      <c r="F115" s="15"/>
+      <c r="G115" s="15"/>
+      <c r="H115" s="87"/>
+      <c r="L115" s="10"/>
+      <c r="M115" s="10"/>
+      <c r="N115" s="10"/>
+      <c r="O115" s="10"/>
+      <c r="P115" s="10"/>
+      <c r="Q115" s="10"/>
+      <c r="R115" s="10"/>
+      <c r="S115" s="10"/>
+      <c r="T115" s="10"/>
+      <c r="U115" s="10"/>
+    </row>
+    <row r="116" spans="1:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="33"/>
+      <c r="B116" s="10"/>
+      <c r="C116" s="10"/>
+      <c r="D116" s="33"/>
+      <c r="E116" s="10"/>
+      <c r="F116" s="15"/>
+      <c r="G116" s="15"/>
+      <c r="H116" s="87"/>
+      <c r="L116" s="10"/>
+      <c r="M116" s="10"/>
+      <c r="N116" s="10"/>
+      <c r="O116" s="10"/>
+      <c r="P116" s="10"/>
+      <c r="Q116" s="10"/>
+      <c r="R116" s="10"/>
+      <c r="S116" s="10"/>
+      <c r="T116" s="10"/>
+      <c r="U116" s="10"/>
+    </row>
+    <row r="117" spans="1:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="33"/>
+      <c r="B117" s="10"/>
+      <c r="C117" s="10"/>
+      <c r="D117" s="33"/>
+      <c r="E117" s="10"/>
+      <c r="F117" s="15"/>
+      <c r="G117" s="15"/>
+      <c r="H117" s="87"/>
+      <c r="L117" s="10"/>
+      <c r="M117" s="10"/>
+      <c r="N117" s="10"/>
+      <c r="O117" s="10"/>
+      <c r="P117" s="10"/>
+      <c r="Q117" s="10"/>
+      <c r="R117" s="10"/>
+      <c r="S117" s="10"/>
+      <c r="T117" s="10"/>
+      <c r="U117" s="10"/>
+    </row>
+    <row r="118" spans="1:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="33"/>
+      <c r="B118" s="10"/>
+      <c r="C118" s="10"/>
+      <c r="D118" s="33"/>
+      <c r="E118" s="10"/>
+      <c r="F118" s="15"/>
+      <c r="G118" s="15"/>
+      <c r="H118" s="87"/>
+      <c r="L118" s="10"/>
+      <c r="M118" s="10"/>
+      <c r="N118" s="10"/>
+      <c r="O118" s="10"/>
+      <c r="P118" s="10"/>
+      <c r="Q118" s="10"/>
+      <c r="R118" s="10"/>
+      <c r="S118" s="10"/>
+      <c r="T118" s="10"/>
+      <c r="U118" s="10"/>
+    </row>
+    <row r="119" spans="1:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="33"/>
+      <c r="B119" s="10"/>
+      <c r="C119" s="10"/>
+      <c r="D119" s="33"/>
+      <c r="E119" s="10"/>
+      <c r="F119" s="15"/>
+      <c r="G119" s="15"/>
+      <c r="H119" s="87"/>
+      <c r="L119" s="10"/>
+      <c r="M119" s="10"/>
+      <c r="N119" s="10"/>
+      <c r="O119" s="10"/>
+      <c r="P119" s="10"/>
+      <c r="Q119" s="10"/>
+      <c r="R119" s="10"/>
+      <c r="S119" s="10"/>
+      <c r="T119" s="10"/>
+      <c r="U119" s="10"/>
+    </row>
+    <row r="120" spans="1:21" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="33"/>
+      <c r="B120" s="10"/>
+      <c r="C120" s="10"/>
+      <c r="D120" s="33"/>
+      <c r="E120" s="10"/>
+      <c r="F120" s="15"/>
+      <c r="G120" s="15"/>
+      <c r="H120" s="87"/>
+      <c r="L120" s="10"/>
+      <c r="M120" s="10"/>
+      <c r="N120" s="10"/>
+      <c r="O120" s="10"/>
+      <c r="P120" s="10"/>
+      <c r="Q120" s="10"/>
+      <c r="R120" s="10"/>
+      <c r="S120" s="10"/>
+      <c r="T120" s="10"/>
+      <c r="U120" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:M24" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A6:M41" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="5">
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="H5:M5"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8" xr:uid="{04A5F538-72D8-41D5-9E01-B43CC7EBC49D}">
-      <formula1>$J$33:$J$35</formula1>
+  <dataValidations disablePrompts="1" count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7:H18" xr:uid="{A0E3F123-E765-4412-9B48-C22114FCBB03}">
+      <formula1>$J$50:$J$52</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9:H21" xr:uid="{032FCD60-9BCB-4D91-9EB5-D44BDB607256}">
-      <formula1>$D$40:$D$41</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19:H38" xr:uid="{97EE823D-A976-42D1-AE4F-7DB38488E151}">
+      <formula1>$D$57:$D$58</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
